--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. STARLABS MORÓN.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. STARLABS MORÓN.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>38.4409</v>
+        <v>54.1636</v>
       </c>
       <c r="E2" t="n">
-        <v>33.3287</v>
+        <v>46.556</v>
       </c>
       <c r="F2" t="n">
-        <v>5.112200000000001</v>
+        <v>7.607700000000001</v>
       </c>
       <c r="G2" t="n">
         <v>31.882</v>
@@ -610,13 +610,13 @@
         <v>52.6538</v>
       </c>
       <c r="S2" t="n">
-        <v>-20.3267</v>
+        <v>-4.604</v>
       </c>
       <c r="T2" t="n">
-        <v>-21.3281</v>
+        <v>-8.1008</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0011</v>
+        <v>3.4962</v>
       </c>
       <c r="V2" t="n">
         <v>11.6927</v>
@@ -643,13 +643,13 @@
         <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>36.5133</v>
+        <v>29.9635</v>
       </c>
       <c r="E3" t="n">
-        <v>29.504</v>
+        <v>23.9875</v>
       </c>
       <c r="F3" t="n">
-        <v>7.0097</v>
+        <v>5.976000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>21.3365</v>
@@ -688,13 +688,13 @@
         <v>31.2176</v>
       </c>
       <c r="S3" t="n">
-        <v>10.7277</v>
+        <v>4.1785</v>
       </c>
       <c r="T3" t="n">
-        <v>4.019600000000001</v>
+        <v>-1.4963</v>
       </c>
       <c r="U3" t="n">
-        <v>6.7082</v>
+        <v>5.6744</v>
       </c>
       <c r="V3" t="n">
         <v>19.2251</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. CORREIA</t>
+          <t>A. BURGOS CABALLERO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>19.635</v>
+        <v>15.5025</v>
       </c>
       <c r="E4" t="n">
-        <v>13.4651</v>
+        <v>16.7359</v>
       </c>
       <c r="F4" t="n">
-        <v>6.169700000000002</v>
+        <v>-1.233</v>
       </c>
       <c r="G4" t="n">
-        <v>2.640000000000001</v>
+        <v>-2.545999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>10.9213</v>
+        <v>14.1425</v>
       </c>
       <c r="I4" t="n">
-        <v>-8.281599999999999</v>
+        <v>-16.6885</v>
       </c>
       <c r="J4" t="n">
-        <v>28.5534</v>
+        <v>27.325</v>
       </c>
       <c r="K4" t="n">
-        <v>24.544</v>
+        <v>27.9877</v>
       </c>
       <c r="L4" t="n">
-        <v>4.0098</v>
+        <v>-0.6623999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-25.9135</v>
+        <v>-29.871</v>
       </c>
       <c r="N4" t="n">
-        <v>-13.6222</v>
+        <v>-13.8451</v>
       </c>
       <c r="O4" t="n">
-        <v>-12.291</v>
+        <v>-16.0261</v>
       </c>
       <c r="P4" t="n">
-        <v>-6.6598</v>
+        <v>11.0302</v>
       </c>
       <c r="Q4" t="n">
-        <v>-40.5832</v>
+        <v>-33.0908</v>
       </c>
       <c r="R4" t="n">
-        <v>33.9234</v>
+        <v>44.1209</v>
       </c>
       <c r="S4" t="n">
-        <v>41.8828</v>
+        <v>1.9947</v>
       </c>
       <c r="T4" t="n">
-        <v>26.3088</v>
+        <v>-2.0693</v>
       </c>
       <c r="U4" t="n">
-        <v>15.574</v>
+        <v>4.064</v>
       </c>
       <c r="V4" t="n">
-        <v>-18.2278</v>
+        <v>5.0237</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.8137999999999999</v>
+        <v>24.5714</v>
       </c>
       <c r="X4" t="n">
-        <v>-17.4139</v>
+        <v>-19.5474</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. BURGOS CABALLERO</t>
+          <t>A. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>15.062</v>
+        <v>6.524200000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>18.9902</v>
+        <v>7.964700000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.9282</v>
+        <v>-1.4406</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.545999999999999</v>
+        <v>23.4112</v>
       </c>
       <c r="H5" t="n">
-        <v>14.1425</v>
+        <v>4.736700000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-16.6885</v>
+        <v>18.6747</v>
       </c>
       <c r="J5" t="n">
-        <v>27.325</v>
+        <v>49.8001</v>
       </c>
       <c r="K5" t="n">
-        <v>27.9877</v>
+        <v>22.5</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6623999999999999</v>
+        <v>27.3</v>
       </c>
       <c r="M5" t="n">
-        <v>-29.871</v>
+        <v>-26.3884</v>
       </c>
       <c r="N5" t="n">
-        <v>-13.8451</v>
+        <v>-17.7632</v>
       </c>
       <c r="O5" t="n">
-        <v>-16.0261</v>
+        <v>-8.6252</v>
       </c>
       <c r="P5" t="n">
-        <v>11.0302</v>
+        <v>-18.3143</v>
       </c>
       <c r="Q5" t="n">
-        <v>-33.0908</v>
+        <v>-59.3139</v>
       </c>
       <c r="R5" t="n">
-        <v>44.1209</v>
+        <v>40.9992</v>
       </c>
       <c r="S5" t="n">
-        <v>1.554</v>
+        <v>3.3234</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1852999999999998</v>
+        <v>-3.148</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3688</v>
+        <v>6.471</v>
       </c>
       <c r="V5" t="n">
-        <v>5.0237</v>
+        <v>-1.8963</v>
       </c>
       <c r="W5" t="n">
-        <v>24.5714</v>
+        <v>20.6265</v>
       </c>
       <c r="X5" t="n">
-        <v>-19.5474</v>
+        <v>-22.5229</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8408</v>
+        <v>5.2949</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5531</v>
+        <v>6.8035</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.7123</v>
+        <v>-1.5084</v>
       </c>
       <c r="G6" t="n">
         <v>3.0363</v>
@@ -922,13 +922,13 @@
         <v>4.3704</v>
       </c>
       <c r="S6" t="n">
-        <v>-3.8199</v>
+        <v>-0.3657999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.2213</v>
+        <v>1.0289</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.5986</v>
+        <v>-1.3946</v>
       </c>
       <c r="V6" t="n">
         <v>1.1674</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. PAREJO CAMACHO</t>
+          <t>J. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4544</v>
+        <v>4.488499999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-7.258700000000001</v>
+        <v>7.452</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8043</v>
+        <v>-2.9634</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.3347</v>
+        <v>18.3322</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2613</v>
+        <v>13.41</v>
       </c>
       <c r="I7" t="n">
-        <v>-7.596200000000001</v>
+        <v>4.9222</v>
       </c>
       <c r="J7" t="n">
-        <v>-7.8157</v>
+        <v>37.6654</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3686</v>
+        <v>24.6648</v>
       </c>
       <c r="L7" t="n">
-        <v>-9.184099999999999</v>
+        <v>13.0006</v>
       </c>
       <c r="M7" t="n">
-        <v>1.4809</v>
+        <v>-19.3333</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1070000000000002</v>
+        <v>-11.2551</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5879</v>
+        <v>-8.0784</v>
       </c>
       <c r="P7" t="n">
-        <v>3.3299</v>
+        <v>-9.573399999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.7461</v>
+        <v>-37.6695</v>
       </c>
       <c r="R7" t="n">
-        <v>7.076000000000001</v>
+        <v>28.0958</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.1683</v>
+        <v>-0.7535000000000002</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4732000000000001</v>
+        <v>-2.0966</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.6947</v>
+        <v>1.3428</v>
       </c>
       <c r="V7" t="n">
-        <v>3.7183</v>
+        <v>-3.5167</v>
       </c>
       <c r="W7" t="n">
-        <v>4.7762</v>
+        <v>9.5525</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0579</v>
+        <v>-13.0694</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MARIN ORTEGA</t>
+          <t>L. PAREJO CAMACHO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.907999999999999</v>
+        <v>0.5139999999999998</v>
       </c>
       <c r="E8" t="n">
-        <v>1.325400000000002</v>
+        <v>-6.9559</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.2336</v>
+        <v>7.4702</v>
       </c>
       <c r="G8" t="n">
-        <v>23.4112</v>
+        <v>-6.3347</v>
       </c>
       <c r="H8" t="n">
-        <v>4.736700000000001</v>
+        <v>1.2613</v>
       </c>
       <c r="I8" t="n">
-        <v>18.6747</v>
+        <v>-7.596200000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>49.8001</v>
+        <v>-7.8157</v>
       </c>
       <c r="K8" t="n">
-        <v>22.5</v>
+        <v>1.3686</v>
       </c>
       <c r="L8" t="n">
-        <v>27.3</v>
+        <v>-9.184099999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-26.3884</v>
+        <v>1.4809</v>
       </c>
       <c r="N8" t="n">
-        <v>-17.7632</v>
+        <v>-0.1070000000000002</v>
       </c>
       <c r="O8" t="n">
-        <v>-8.6252</v>
+        <v>1.5879</v>
       </c>
       <c r="P8" t="n">
-        <v>-18.3143</v>
+        <v>3.3299</v>
       </c>
       <c r="Q8" t="n">
-        <v>-59.3139</v>
+        <v>-3.7461</v>
       </c>
       <c r="R8" t="n">
-        <v>40.9992</v>
+        <v>7.076000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>-5.1087</v>
+        <v>-0.1994000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-9.7872</v>
+        <v>-0.1702</v>
       </c>
       <c r="U8" t="n">
-        <v>4.6782</v>
+        <v>-0.02909999999999996</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.8963</v>
+        <v>3.7183</v>
       </c>
       <c r="W8" t="n">
-        <v>20.6265</v>
+        <v>4.7762</v>
       </c>
       <c r="X8" t="n">
-        <v>-22.5229</v>
+        <v>-1.0579</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. RODRIGUEZ CALZADO</t>
+          <t>G. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9615</v>
+        <v>-0.2736000000000005</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5592</v>
+        <v>2.9389</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4023</v>
+        <v>-3.212499999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4778</v>
+        <v>-5.442</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1919</v>
+        <v>3.5304</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2859</v>
+        <v>-8.972499999999998</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4288</v>
+        <v>13.2135</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>10.613</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.4288</v>
+        <v>2.600199999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.04899999999999999</v>
+        <v>-18.6551</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1919</v>
+        <v>-7.082799999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1429</v>
+        <v>-11.5724</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>11.2384</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-18.5225</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>29.7611</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2537</v>
+        <v>4.5371</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1304</v>
+        <v>1.7737</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1233</v>
+        <v>2.7632</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.23</v>
+        <v>-10.6071</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>6.4744</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.23</v>
+        <v>-17.0813</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. FERNANDEZ DIAZ</t>
+          <t>D. RODRIGUEZ CALZADO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.809600000000001</v>
+        <v>-1.9321</v>
       </c>
       <c r="E10" t="n">
-        <v>2.710500000000001</v>
+        <v>-1.5592</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.519900000000001</v>
+        <v>-0.3729</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.442</v>
+        <v>-1.4778</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5304</v>
+        <v>-0.1919</v>
       </c>
       <c r="I10" t="n">
-        <v>-8.972499999999998</v>
+        <v>-1.2859</v>
       </c>
       <c r="J10" t="n">
-        <v>13.2135</v>
+        <v>-1.4288</v>
       </c>
       <c r="K10" t="n">
-        <v>10.613</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2.600199999999999</v>
+        <v>-1.4288</v>
       </c>
       <c r="M10" t="n">
-        <v>-18.6551</v>
+        <v>-0.04899999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-7.082799999999999</v>
+        <v>-0.1919</v>
       </c>
       <c r="O10" t="n">
-        <v>-11.5724</v>
+        <v>0.1429</v>
       </c>
       <c r="P10" t="n">
-        <v>11.2384</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-18.5225</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>29.7611</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.001</v>
+        <v>-0.2243</v>
       </c>
       <c r="T10" t="n">
-        <v>1.5451</v>
+        <v>-0.1304</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5445999999999999</v>
+        <v>-0.0939</v>
       </c>
       <c r="V10" t="n">
-        <v>-10.6071</v>
+        <v>-0.23</v>
       </c>
       <c r="W10" t="n">
-        <v>6.4744</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-17.0813</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. MARIN ORTEGA</t>
+          <t>Z. WILLIAMS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9907</v>
+        <v>-2.0605</v>
       </c>
       <c r="E11" t="n">
-        <v>1.436999999999999</v>
+        <v>1.5704</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.4277</v>
+        <v>-3.6306</v>
       </c>
       <c r="G11" t="n">
-        <v>18.3322</v>
+        <v>5.2473</v>
       </c>
       <c r="H11" t="n">
-        <v>13.41</v>
+        <v>6.4998</v>
       </c>
       <c r="I11" t="n">
-        <v>4.9222</v>
+        <v>-1.2523</v>
       </c>
       <c r="J11" t="n">
-        <v>37.6654</v>
+        <v>28.0053</v>
       </c>
       <c r="K11" t="n">
-        <v>24.6648</v>
+        <v>18.1013</v>
       </c>
       <c r="L11" t="n">
-        <v>13.0006</v>
+        <v>9.9039</v>
       </c>
       <c r="M11" t="n">
-        <v>-19.3333</v>
+        <v>-22.7577</v>
       </c>
       <c r="N11" t="n">
-        <v>-11.2551</v>
+        <v>-11.6012</v>
       </c>
       <c r="O11" t="n">
-        <v>-8.0784</v>
+        <v>-11.1562</v>
       </c>
       <c r="P11" t="n">
-        <v>-9.573399999999999</v>
+        <v>-5.619299999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-37.6695</v>
+        <v>-32.4666</v>
       </c>
       <c r="R11" t="n">
-        <v>28.0958</v>
+        <v>26.8473</v>
       </c>
       <c r="S11" t="n">
-        <v>-9.2323</v>
+        <v>1.1098</v>
       </c>
       <c r="T11" t="n">
-        <v>-8.111599999999999</v>
+        <v>-0.7791</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1213</v>
+        <v>1.889</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.5167</v>
+        <v>-2.7984</v>
       </c>
       <c r="W11" t="n">
-        <v>9.5525</v>
+        <v>6.8106</v>
       </c>
       <c r="X11" t="n">
-        <v>-13.0694</v>
+        <v>-9.6091</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Z. WILLIAMS</t>
+          <t>S. CORREIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4497</v>
+        <v>-5.735999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1772000000000009</v>
+        <v>-4.4761</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.2726</v>
+        <v>-1.2603</v>
       </c>
       <c r="G12" t="n">
-        <v>5.2473</v>
+        <v>2.640000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>6.4998</v>
+        <v>10.9213</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2523</v>
+        <v>-8.281599999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>28.0053</v>
+        <v>28.5534</v>
       </c>
       <c r="K12" t="n">
-        <v>18.1013</v>
+        <v>24.544</v>
       </c>
       <c r="L12" t="n">
-        <v>9.9039</v>
+        <v>4.0098</v>
       </c>
       <c r="M12" t="n">
-        <v>-22.7577</v>
+        <v>-25.9135</v>
       </c>
       <c r="N12" t="n">
-        <v>-11.6012</v>
+        <v>-13.6222</v>
       </c>
       <c r="O12" t="n">
-        <v>-11.1562</v>
+        <v>-12.291</v>
       </c>
       <c r="P12" t="n">
-        <v>-5.619299999999999</v>
+        <v>-6.6598</v>
       </c>
       <c r="Q12" t="n">
-        <v>-32.4666</v>
+        <v>-40.5832</v>
       </c>
       <c r="R12" t="n">
-        <v>26.8473</v>
+        <v>33.9234</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.2797</v>
+        <v>16.5114</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.526</v>
+        <v>8.3674</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2468999999999999</v>
+        <v>8.143800000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.7984</v>
+        <v>-18.2278</v>
       </c>
       <c r="W12" t="n">
-        <v>6.8106</v>
+        <v>-0.8137999999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-9.6091</v>
+        <v>-17.4139</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>17</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.928799999999999</v>
+        <v>-8.289699999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.6714</v>
+        <v>-5.335900000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.257099999999999</v>
+        <v>-2.9539</v>
       </c>
       <c r="G13" t="n">
         <v>-11.1082</v>
@@ -1468,13 +1468,13 @@
         <v>20.6036</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8634</v>
+        <v>3.5023</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8011999999999999</v>
+        <v>1.1369</v>
       </c>
       <c r="U13" t="n">
-        <v>2.0625</v>
+        <v>2.3658</v>
       </c>
       <c r="V13" t="n">
         <v>-6.9272</v>
@@ -1501,13 +1501,13 @@
         <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>-18.6935</v>
+        <v>-8.9138</v>
       </c>
       <c r="E14" t="n">
-        <v>-21.4166</v>
+        <v>-15.3596</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7233</v>
+        <v>6.4459</v>
       </c>
       <c r="G14" t="n">
         <v>-3.247000000000001</v>
@@ -1546,13 +1546,13 @@
         <v>27.8878</v>
       </c>
       <c r="S14" t="n">
-        <v>-10.8748</v>
+        <v>-1.0954</v>
       </c>
       <c r="T14" t="n">
-        <v>-11.4845</v>
+        <v>-5.4278</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6095999999999999</v>
+        <v>4.3322</v>
       </c>
       <c r="V14" t="n">
         <v>-4.7797</v>
@@ -1579,16 +1579,16 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>65.29579999999999</v>
+        <v>89.24549999999998</v>
       </c>
       <c r="E15" t="n">
-        <v>69.23089999999999</v>
+        <v>80.32220000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.934499999999996</v>
+        <v>8.924200000000003</v>
       </c>
       <c r="G15" t="n">
-        <v>75.72979999999998</v>
+        <v>75.7298</v>
       </c>
       <c r="H15" t="n">
         <v>60.4221</v>
@@ -1603,7 +1603,7 @@
         <v>189.2244</v>
       </c>
       <c r="L15" t="n">
-        <v>98.64260000000002</v>
+        <v>98.6426</v>
       </c>
       <c r="M15" t="n">
         <v>-212.1356</v>
@@ -1615,22 +1615,22 @@
         <v>-83.3331</v>
       </c>
       <c r="P15" t="n">
-        <v>-6.243899999999998</v>
+        <v>-6.243899999999996</v>
       </c>
       <c r="Q15" t="n">
-        <v>-353.8019</v>
+        <v>-353.8018999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>347.5568999999999</v>
+        <v>347.5569</v>
       </c>
       <c r="S15" t="n">
-        <v>3.964800000000009</v>
+        <v>27.9148</v>
       </c>
       <c r="T15" t="n">
-        <v>-22.20229999999999</v>
+        <v>-11.1116</v>
       </c>
       <c r="U15" t="n">
-        <v>26.1668</v>
+        <v>39.0248</v>
       </c>
       <c r="V15" t="n">
         <v>-8.156000000000006</v>
